--- a/artfynd/A 22626-2021 artfynd.xlsx
+++ b/artfynd/A 22626-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127127739</v>
       </c>
       <c r="B2" t="n">
-        <v>91973</v>
+        <v>92047</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127127737</v>
       </c>
       <c r="B3" t="n">
-        <v>91603</v>
+        <v>91677</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>127127521</v>
       </c>
       <c r="B4" t="n">
-        <v>90680</v>
+        <v>90754</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22626-2021 artfynd.xlsx
+++ b/artfynd/A 22626-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127127739</v>
       </c>
       <c r="B2" t="n">
-        <v>92047</v>
+        <v>92053</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127127737</v>
       </c>
       <c r="B3" t="n">
-        <v>91677</v>
+        <v>91683</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>127127521</v>
       </c>
       <c r="B4" t="n">
-        <v>90754</v>
+        <v>90760</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22626-2021 artfynd.xlsx
+++ b/artfynd/A 22626-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127127739</v>
       </c>
       <c r="B2" t="n">
-        <v>92053</v>
+        <v>92054</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127127737</v>
       </c>
       <c r="B3" t="n">
-        <v>91683</v>
+        <v>91684</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>127127521</v>
       </c>
       <c r="B4" t="n">
-        <v>90760</v>
+        <v>90761</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22626-2021 artfynd.xlsx
+++ b/artfynd/A 22626-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127127739</v>
       </c>
       <c r="B2" t="n">
-        <v>92054</v>
+        <v>92058</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127127737</v>
       </c>
       <c r="B3" t="n">
-        <v>91684</v>
+        <v>91688</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>127127521</v>
       </c>
       <c r="B4" t="n">
-        <v>90761</v>
+        <v>90765</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22626-2021 artfynd.xlsx
+++ b/artfynd/A 22626-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127127739</v>
       </c>
       <c r="B2" t="n">
-        <v>92058</v>
+        <v>92060</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127127737</v>
       </c>
       <c r="B3" t="n">
-        <v>91688</v>
+        <v>91690</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>127127521</v>
       </c>
       <c r="B4" t="n">
-        <v>90765</v>
+        <v>90767</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22626-2021 artfynd.xlsx
+++ b/artfynd/A 22626-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127127739</v>
       </c>
       <c r="B2" t="n">
-        <v>92060</v>
+        <v>92066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127127737</v>
       </c>
       <c r="B3" t="n">
-        <v>91690</v>
+        <v>91696</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>127127521</v>
       </c>
       <c r="B4" t="n">
-        <v>90767</v>
+        <v>90773</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22626-2021 artfynd.xlsx
+++ b/artfynd/A 22626-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127127739</v>
       </c>
       <c r="B2" t="n">
-        <v>92066</v>
+        <v>92069</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127127737</v>
       </c>
       <c r="B3" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>127127521</v>
       </c>
       <c r="B4" t="n">
-        <v>90773</v>
+        <v>90776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22626-2021 artfynd.xlsx
+++ b/artfynd/A 22626-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127127739</v>
       </c>
       <c r="B2" t="n">
-        <v>92069</v>
+        <v>92077</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127127737</v>
       </c>
       <c r="B3" t="n">
-        <v>91699</v>
+        <v>91707</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>127127521</v>
       </c>
       <c r="B4" t="n">
-        <v>90776</v>
+        <v>90784</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22626-2021 artfynd.xlsx
+++ b/artfynd/A 22626-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127127739</v>
       </c>
       <c r="B2" t="n">
-        <v>92077</v>
+        <v>92047</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127127737</v>
       </c>
       <c r="B3" t="n">
-        <v>91707</v>
+        <v>91677</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>127127521</v>
       </c>
       <c r="B4" t="n">
-        <v>90784</v>
+        <v>90754</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22626-2021 artfynd.xlsx
+++ b/artfynd/A 22626-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127127739</v>
       </c>
       <c r="B2" t="n">
-        <v>92047</v>
+        <v>92077</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127127737</v>
       </c>
       <c r="B3" t="n">
-        <v>91677</v>
+        <v>91707</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>127127521</v>
       </c>
       <c r="B4" t="n">
-        <v>90754</v>
+        <v>90784</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
